--- a/artfynd/A 16769-2026 artfynd.xlsx
+++ b/artfynd/A 16769-2026 artfynd.xlsx
@@ -1198,50 +1198,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133217703</v>
+        <v>133283204</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>96468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brännebäck, Brännebäck, Sm</t>
+          <t>Brännebäck, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579941</v>
+        <v>579893</v>
       </c>
       <c r="R7" t="n">
-        <v>6315004</v>
+        <v>6314859</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,8 +1281,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>På mycket nedbruten granlåga</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1300,49 +1310,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133283204</v>
+        <v>133217703</v>
       </c>
       <c r="B8" t="n">
-        <v>96468</v>
+        <v>57955</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brännebäck, Sm</t>
+          <t>Brännebäck, Brännebäck, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579893</v>
+        <v>579941</v>
       </c>
       <c r="R8" t="n">
-        <v>6314859</v>
+        <v>6315004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,19 +1394,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>På mycket nedbruten granlåga</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 16769-2026 artfynd.xlsx
+++ b/artfynd/A 16769-2026 artfynd.xlsx
@@ -1198,49 +1198,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133283204</v>
+        <v>133217703</v>
       </c>
       <c r="B7" t="n">
-        <v>96468</v>
+        <v>57955</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brännebäck, Sm</t>
+          <t>Brännebäck, Brännebäck, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579893</v>
+        <v>579941</v>
       </c>
       <c r="R7" t="n">
-        <v>6314859</v>
+        <v>6315004</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,19 +1282,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>På mycket nedbruten granlåga</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1310,50 +1300,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133217703</v>
+        <v>133283204</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>96468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brännebäck, Brännebäck, Sm</t>
+          <t>Brännebäck, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579941</v>
+        <v>579893</v>
       </c>
       <c r="R8" t="n">
-        <v>6315004</v>
+        <v>6314859</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,8 +1383,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>På mycket nedbruten granlåga</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 16769-2026 artfynd.xlsx
+++ b/artfynd/A 16769-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>133221539</v>
       </c>
       <c r="B3" t="n">
-        <v>96718</v>
+        <v>96720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>133222140</v>
       </c>
       <c r="B4" t="n">
-        <v>96468</v>
+        <v>96470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>133222057</v>
       </c>
       <c r="B6" t="n">
-        <v>96564</v>
+        <v>96566</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>133283204</v>
       </c>
       <c r="B8" t="n">
-        <v>96468</v>
+        <v>96470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16769-2026 artfynd.xlsx
+++ b/artfynd/A 16769-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>133221539</v>
       </c>
       <c r="B3" t="n">
-        <v>96720</v>
+        <v>96728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>133222140</v>
       </c>
       <c r="B4" t="n">
-        <v>96470</v>
+        <v>96478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>133222057</v>
       </c>
       <c r="B6" t="n">
-        <v>96566</v>
+        <v>96574</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>133283204</v>
       </c>
       <c r="B8" t="n">
-        <v>96470</v>
+        <v>96478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16769-2026 artfynd.xlsx
+++ b/artfynd/A 16769-2026 artfynd.xlsx
@@ -1198,50 +1198,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133217703</v>
+        <v>133283204</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>96478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brännebäck, Brännebäck, Sm</t>
+          <t>Brännebäck, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579941</v>
+        <v>579893</v>
       </c>
       <c r="R7" t="n">
-        <v>6315004</v>
+        <v>6314859</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,8 +1281,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>På mycket nedbruten granlåga</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1300,49 +1310,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133283204</v>
+        <v>133217703</v>
       </c>
       <c r="B8" t="n">
-        <v>96478</v>
+        <v>57955</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brännebäck, Sm</t>
+          <t>Brännebäck, Brännebäck, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579893</v>
+        <v>579941</v>
       </c>
       <c r="R8" t="n">
-        <v>6314859</v>
+        <v>6315004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,19 +1394,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>På mycket nedbruten granlåga</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 16769-2026 artfynd.xlsx
+++ b/artfynd/A 16769-2026 artfynd.xlsx
@@ -675,48 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132763559</v>
+        <v>133222057</v>
       </c>
       <c r="B2" t="n">
-        <v>99130</v>
+        <v>96629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Syd Brännebäck, Sm</t>
+          <t>Brännebäck, Brännebäck, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579930</v>
+        <v>579872</v>
       </c>
       <c r="R2" t="n">
-        <v>6314977</v>
+        <v>6314909</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,21 +770,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>barrblandskog där granen blivit kvar efter avverkning runtom i beståndet.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,7 +789,7 @@
         <v>133221539</v>
       </c>
       <c r="B3" t="n">
-        <v>96766</v>
+        <v>96783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +895,7 @@
         <v>133222140</v>
       </c>
       <c r="B4" t="n">
-        <v>96516</v>
+        <v>96533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,53 +994,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133224733</v>
+        <v>133283204</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>96533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ballehäll, Ballehäll, Sm</t>
+          <t>Brännebäck, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579906</v>
+        <v>579893</v>
       </c>
       <c r="R5" t="n">
-        <v>6314830</v>
+        <v>6314859</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,8 +1077,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>På mycket nedbruten granlåga</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1087,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133222057</v>
+        <v>133217703</v>
       </c>
       <c r="B6" t="n">
-        <v>96612</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,36 +1117,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1136,13 +1146,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579872</v>
+        <v>579941</v>
       </c>
       <c r="R6" t="n">
-        <v>6314909</v>
+        <v>6315004</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133283204</v>
+        <v>133224733</v>
       </c>
       <c r="B7" t="n">
-        <v>96516</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,41 +1219,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brännebäck, Sm</t>
+          <t>Ballehäll, Ballehäll, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579893</v>
+        <v>579906</v>
       </c>
       <c r="R7" t="n">
-        <v>6314859</v>
+        <v>6314830</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1281,19 +1292,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>På mycket nedbruten granlåga</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1310,50 +1310,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133217703</v>
+        <v>132763559</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>99195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brännebäck, Brännebäck, Sm</t>
+          <t>Syd Brännebäck, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579941</v>
+        <v>579930</v>
       </c>
       <c r="R8" t="n">
-        <v>6315004</v>
+        <v>6314977</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,12 +1375,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,16 +1391,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>barrblandskog där granen blivit kvar efter avverkning runtom i beståndet.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 16769-2026 artfynd.xlsx
+++ b/artfynd/A 16769-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133222057</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133221539</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133222140</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133283204</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133217703</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133224733</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,8 +1444,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132763559</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>